--- a/test_data/WTA/WTA Calculator - Repatriation Calculator/WTA Calculator - Repatriation Calculator_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Calculator - Repatriation Calculator/WTA Calculator - Repatriation Calculator_Test_Cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,11 +47,6 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -65,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -74,9 +69,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -444,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -696,93 +688,212 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>RepCalc_04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Selecting a Source Jurisdiction sets the Repatriation Amount currency badge</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Before any selection the amount field shows a '--' placeholder badge; selecting Australia as Source Jurisdiction must update it to 'AUD' - a real dependent-field effect.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Repatriation Calculator.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Repatriation Calculator
+2. Verify the currency badge starts as '--'
+3. Select Australia as Source Jurisdiction
+4. Verify the currency badge becomes 'AUD'</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Before any selection the amount field shows a '--' placeholder badge; selecting Australia as Source Jurisdiction must update it to 'AUD' - a real dependent-field effect.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>The currency badge correctly updated from '--' to 'AUD' as a dependent effect of the Source Jurisdiction selection.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Currency badge updates from '--' to 'AUD' after selecting Australia</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Selecting both jurisdictions renders the 'Relief from double taxation' panel</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>With Australia (source) and Singapore (residence) selected, a 'Relief from double taxation: Singapore' panel must render.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Repatriation Calculator.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Source: Australia, Residence: Singapore</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Repatriation Calculator
+2. Select Australia then Singapore
+3. Verify the Relief panel heading</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>With Australia (source) and Singapore (residence) selected, a 'Relief from double taxation: Singapore' panel must render.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Selecting both jurisdictions correctly rendered the Relief panel.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Relief from double taxation: Singapore' panel is visible</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>RepCalc_06</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Relief methods listed match the real AU-SG treaty data</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>The Relief panel's 'Relief methods' list for Australia/Singapore must show both 'Exemption' and 'Credit' - confirmed live, real treaty content, not placeholder text.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia+Singapore selected on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Source: Australia, Residence: Singapore</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select Australia and Singapore
 2. Verify the Relief methods list shows 'Exemption' and 'Credit'</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>The Relief panel's 'Relief methods' list for Australia/Singapore must show both 'Exemption' and 'Credit' - confirmed live, real treaty content, not placeholder text.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>The Relief methods list correctly showed both 'Exemption' and 'Credit' for AU/SG.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>[PASS] Relief methods list shows 'Exemption' and 'Credit'</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>RepCalc_07</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>'Get Forms' becomes enabled once a Source Jurisdiction is selected</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>'Get Forms' must stay disabled with nothing selected, and become enabled as soon as a Source Jurisdiction alone is picked - confirmed live this does NOT require a Residence Jurisdiction too (unlike Generate Memo/Add to Project, which need the full calculation chain); it stays enabled once Residence is added as well.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Source: Australia, Residence: Singapore</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator
 2. Verify 'Get Forms' starts disabled
@@ -791,415 +902,651 @@
 5. Select Singapore as Residence Jurisdiction and verify it stays enabled</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>'Get Forms' must stay disabled with nothing selected, and become enabled as soon as a Source Jurisdiction alone is picked - confirmed live this does NOT require a Residence Jurisdiction too (unlike Generate Memo/Add to Project, which need the full calculation chain); it stays enabled once Residence is added as well.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>'Get Forms' correctly enabled as soon as Source Jurisdiction alone was selected, and stayed enabled once Residence Jurisdiction was added too.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Get Forms' is disabled with nothing selected
 [PASS] 'Get Forms' becomes enabled once Source Jurisdiction alone is selected
 [PASS] 'Get Forms' remains enabled once Residence Jurisdiction is also selected</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>RepCalc_08</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Selecting the same country for both jurisdictions shows a blocking message</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Selecting 'Australia' as both Source and Residence Jurisdiction must trigger a modal reading 'Source and Residence Jurisdiction must be different.' with only a Cancel action - confirmed live real validation, not a crash or silent no-op.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected as Source Jurisdiction.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Source: Australia, Residence: Australia</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select Australia as Source
 2. Select Australia as Residence too
 3. Verify the blocking message modal</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Selecting 'Australia' as both Source and Residence Jurisdiction must trigger a modal reading 'Source and Residence Jurisdiction must be different.' with only a Cancel action - confirmed live real validation, not a crash or silent no-op.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Selecting the same country for both jurisdictions correctly triggered the real blocking validation message.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>[PASS] The same-jurisdiction validation modal shows the expected message with only Cancel</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Repatriation Amount rejects a negative sign (real keystrokes)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Typing '-5000' (as real keystrokes, not .fill()) into Repatriation Amount must strip the minus sign - the field never holds a negative value.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Repatriation Calculator.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Typed: -5000</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Repatriation Calculator
+2. Type '-5000' into Repatriation Amount
+3. Verify the minus sign was stripped</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Typing '-5000' (as real keystrokes, not .fill()) into Repatriation Amount must strip the minus sign - the field never holds a negative value.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Typing '-5000' correctly produced a non-negative value ('5,000').</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Repatriation Amount never holds a negative value</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Repatriation Amount strips non-digit characters</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'abc123' (real keystrokes) must leave only the digits ('123').</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Repatriation Calculator.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Typed: abc123</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Repatriation Calculator
+2. Type 'abc123' into Repatriation Amount
+3. Verify only '123' remains</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'abc123' (real keystrokes) must leave only the digits ('123').</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Typing 'abc123' correctly left only the digits ('123').</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Only the digits '123' remain after typing 'abc123'</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>RepCalc_11</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Repatriation Amount treats '0' as no value</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Typing '0' alone must leave the field empty, confirming zero is rejected as a valid repatriation amount rather than being accepted as a literal zero.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Typed: 0</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Repatriation Calculator
 2. Type '0' into Repatriation Amount
 3. Verify the field is empty</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Typing '0' alone must leave the field empty, confirming zero is rejected as a valid repatriation amount rather than being accepted as a literal zero.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Typing '0' correctly left the amount field empty, confirming zero is treated as no value.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>[PASS] Typing '0' leaves Repatriation Amount empty</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Repatriation Amount accepts decimal values</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Typing '12.345' must be accepted as-is (decimal repatriation amounts are valid).</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Repatriation Calculator.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Typed: 12.345</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Repatriation Calculator
+2. Type '12.345' into Repatriation Amount
+3. Verify the decimal value is retained</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Typing '12.345' must be accepted as-is (decimal repatriation amounts are valid).</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Typing '12.345' was correctly retained as a decimal value.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Decimal value '12.345' is retained</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>RepCalc_13</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Repatriation Amount formats large values with thousands separators</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Typing '1000000000' (one billion) must be accepted and displayed as '1,000,000,000' - confirmed live there is no artificial maximum blocking this.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Typed: 1000000000</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Repatriation Calculator
 2. Type '1000000000' into Repatriation Amount
 3. Verify it is formatted with thousands separators</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Typing '1000000000' (one billion) must be accepted and displayed as '1,000,000,000' - confirmed live there is no artificial maximum blocking this.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>A one-billion repatriation amount was correctly formatted as '1,000,000,000'.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>[PASS] Large value is formatted with thousands separators</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>RepCalc_14</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Income Stream dropdown lists the 5 real categories</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>The Select Income Stream dropdown must list exactly: Dividends, Interest, Royalties, Lease Payments, Technical Service Fees.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>User is logged in, both jurisdictions and an amount set on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select Australia, Singapore and an amount
 2. Open the Select Income Stream dropdown
 3. Verify all 5 categories are listed</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>The Select Income Stream dropdown must list exactly: Dividends, Interest, Royalties, Lease Payments, Technical Service Fees.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>The Income Stream dropdown correctly listed all 5 categories: ['Dividends', 'Interest', 'Royalties', 'Lease Payments', 'Technical Service Fees'].</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>[PASS] Income Stream dropdown lists exactly the 5 expected categories</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Entering amount and income stream renders the results table</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>With Australia/Singapore/100,000/Dividends set, a results table with a 'What is the % of holding in the company?' selector must render.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Repatriation Calculator.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Source: Australia, Residence: Singapore, Amount: 100000, Stream: Dividends</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator
+2. Select Australia, Singapore, enter 100000, select Dividends
+3. Verify the results table with the holding % selector renders</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>With Australia/Singapore/100,000/Dividends set, a results table with a 'What is the % of holding in the company?' selector must render.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>The results table correctly rendered with the holding % selector.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The results table with the holding % question is visible</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>RepCalc_16</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Holding % selector is limited to exactly 1% through 7%</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>The 'What is the % of holding in the company?' dropdown must list exactly ['1%'..'7%'] - a real, confirmed-live data boundary, not a UI truncation.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia/Singapore/100000/Dividends set.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, complete the setup through Income Stream
 2. Open the holding % dropdown
 3. Verify it lists exactly 1% through 7%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>The 'What is the % of holding in the company?' dropdown must list exactly ['1%'..'7%'] - a real, confirmed-live data boundary, not a UI truncation.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>The holding % dropdown correctly listed exactly ['1%', '2%', '3%', '4%', '5%', '6%', '7%'].</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>[PASS] Holding % dropdown lists exactly 1% through 7%</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>RepCalc_17</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>The displayed Treaty Rate matches the live Treaty API</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>With Australia/Singapore/Dividends/7% selected, the UI must show 'Treaty Rate - 15.00%' and 'Your holding type is Portfolio.' - independently verified against GET /api/Treaty?hostCountryCode=AU&amp;partnerCountryCode=SG (WtrDomesticRates[Portfolio Dividend].Rate), not compared against itself.</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Source: Australia, Residence: Singapore, Stream: Dividends, Holding: 7%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, complete AU-&gt;SG/Dividends/7%
 2. Independently fetch the Treaty API for AU/SG
 3. Verify the UI's Treaty Rate matches the API's Portfolio Dividend rate</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>With Australia/Singapore/Dividends/7% selected, the UI must show 'Treaty Rate - 15.00%' and 'Your holding type is Portfolio.' - independently verified against GET /api/Treaty?hostCountryCode=AU&amp;partnerCountryCode=SG (WtrDomesticRates[Portfolio Dividend].Rate), not compared against itself.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>The UI's Treaty Rate ('Treaty Rate - 15.00%') correctly matched the live API's independent value (15.00%).</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>[PASS] UI Treaty Rate matches the independently-fetched API value</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>RepCalc_18</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Withholding tax amount matches an independent Python calculation</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>With amount=100,000, Treaty Rate=15.00% and a user-entered Exchange Rate of 1.2, the computed Withholding tax amount AND Total Tax Due must both equal 100,000 x 0.15 x 1.2 = 18,000 - calculated independently in Python from the known inputs, not read back from the application and compared to itself.</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>User is logged in, AU-&gt;SG/Dividends/7% completed on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Amount: 100000, Treaty Rate: 15%, Exchange Rate: 1.2</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, complete AU-&gt;SG/Dividends/7% with amount 100000
 2. Enter Exchange Rate = 1.2
@@ -1207,59 +1554,235 @@
 4. Verify both the Withholding tax amount and Total Tax Due equal that value</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>With amount=100,000, Treaty Rate=15.00% and a user-entered Exchange Rate of 1.2, the computed Withholding tax amount AND Total Tax Due must both equal 100,000 x 0.15 x 1.2 = 18,000 - calculated independently in Python from the known inputs, not read back from the application and compared to itself.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>The computed amounts (18000, 18000) correctly matched the independent calculation of 18,000 (100,000 x 15% x 1.2).</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>[PASS] Withholding tax amount and Total Tax Due match the independent Python calculation</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Changing the Exchange Rate live-recalculates the computed amounts</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>After computing with Exchange Rate=1.2 (18,000), changing it to 2.0 must update the Withholding tax amount/Total Tax Due to 100,000 x 0.15 x 2.0 = 30,000 without requiring any other field to be re-entered.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, AU-&gt;SG/Dividends/7%/Exchange Rate=1.2 completed.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Exchange Rate changed from 1.2 to 2.0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator, complete the setup with Exchange Rate 1.2
+2. Change the Exchange Rate to 2.0
+3. Verify the computed amounts update to 30,000</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>After computing with Exchange Rate=1.2 (18,000), changing it to 2.0 must update the Withholding tax amount/Total Tax Due to 100,000 x 0.15 x 2.0 = 30,000 without requiring any other field to be re-entered.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Changing the Exchange Rate correctly recalculated the amounts to 30,000.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Changing the Exchange Rate live-recalculates the computed amounts</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>The Rates panel shows the real treaty article text</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>The 'Rates: Australia' panel must show 'Article 8 (1)' and the real treaty wording mentioning 'shall not exceed 15 per centum of the gross amount of the dividends.'</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, AU-&gt;SG/Dividends/7% completed on Repatriation Calculator.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator, complete AU-&gt;SG/Dividends/7%
+2. Verify the Rates panel shows Article 8(1) and the treaty wording</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>The 'Rates: Australia' panel must show 'Article 8 (1)' and the real treaty wording mentioning 'shall not exceed 15 per centum of the gross amount of the dividends.'</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>The Rates panel correctly showed the real Article 8(1) treaty wording.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Rates panel shows the real Article 8(1) treaty text</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Switching Income Stream resets the holding %/rate selection</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>After selecting Dividends and a 7% holding (Treaty Rate 15.00%), switching Income Stream to 'Interest' must clear the previous holding %/rate selection rather than carry stale Dividend-specific data forward.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, AU-&gt;SG/Dividends/7% completed on Repatriation Calculator.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Stream changed from Dividends to Interest</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator, complete AU-&gt;SG/Dividends/7%
+2. Change Income Stream to 'Interest'
+3. Verify the Dividend-specific holding type text is no longer shown</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>After selecting Dividends and a 7% holding (Treaty Rate 15.00%), switching Income Stream to 'Interest' must clear the previous holding %/rate selection rather than carry stale Dividend-specific data forward.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Switching Income Stream correctly reset the previous selection's holding-type text.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Switching Income Stream clears the previous stream's holding selection</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>RepCalc_22</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>'Generate Memo'/'Add to Project' enable only after the full chain completes</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Both buttons must stay disabled through jurisdictions+amount+stream, and only become enabled once a holding % is also selected (the full calculation chain).</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, complete jurisdictions+amount+stream only
 2. Verify Generate Memo/Add to Project are still disabled
@@ -1267,497 +1790,852 @@
 4. Verify both become enabled</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Both buttons must stay disabled through jurisdictions+amount+stream, and only become enabled once a holding % is also selected (the full calculation chain).</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>'Generate Memo'/'Add to Project' correctly followed the full-chain dependency.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>[PASS] Generate Memo/Add to Project disabled before holding % is selected
 [PASS] Generate Memo/Add to Project become enabled once holding % is selected</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>RepCalc_23</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>'Generate Memo' downloads a real, non-empty .docx file</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/Dividends/7% complete, clicking 'Generate Memo' must download a real, non-empty .docx memo.</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>User is logged in, AU-&gt;SG/Dividends/7% completed on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, complete AU-&gt;SG/Dividends/7%
 2. Click 'Generate Memo'
 3. Verify a real, non-empty .docx download completed</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/Dividends/7% complete, clicking 'Generate Memo' must download a real, non-empty .docx memo.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>'Generate Memo' correctly downloaded 'AU_SG_Repatriation_Calculator_Memo.docx' (9067 bytes).</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>'Generate Memo' correctly downloaded 'AU_SG_Repatriation_Calculator_Memo.docx' (9068 bytes).</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>[PASS] Generate Memo produces a real, non-empty .docx file with no failure</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_24</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>'Get Forms' opens a modal with the real, jurisdiction-specific form list</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>With Australia/Singapore selected, clicking 'Get Forms' must open a modal reading 'CIT Returns and WHT deduction/Treaty form of Australia.' with a real Title/Description/Application Date/Last Reviewed/Download table.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia+Singapore selected on Repatriation Calculator.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator, select Australia and Singapore
+2. Click 'Get Forms'
+3. Verify the modal shows the real form list</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>With Australia/Singapore selected, clicking 'Get Forms' must open a modal reading 'CIT Returns and WHT deduction/Treaty form of Australia.' with a real Title/Description/Application Date/Last Reviewed/Download table.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>'Get Forms' correctly opened with the real, jurisdiction-specific form list.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Get Forms' modal shows the real jurisdiction-specific form list</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>A form's download link in 'Get Forms' downloads a real, non-empty file</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Inside the 'Get Forms' modal, clicking the first 'English' download link must trigger a real, non-empty file download.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia+Singapore selected, 'Get Forms' modal open.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator, select Australia+Singapore, open 'Get Forms'
+2. Click the first 'English' download link
+3. Verify a real, non-empty download completed</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Inside the 'Get Forms' modal, clicking the first 'English' download link must trigger a real, non-empty file download.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>The form download link correctly downloaded 'AU_Form__NAT_0656_06_2025_English_pdf.pdf' (1056759 bytes).</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The form's download link produces a real, non-empty file with no failure</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>RepCalc_26</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>The 'Get Forms' modal's Close button closes it</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>With the 'Get Forms' modal open, clicking 'Close' must close it.</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia+Singapore selected, 'Get Forms' modal open.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select Australia+Singapore, open 'Get Forms'
 2. Click 'Close'
 3. Verify the modal is closed</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>With the 'Get Forms' modal open, clicking 'Close' must close it.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>The 'Get Forms' modal's Close button correctly closed it.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>[PASS] The 'Get Forms' modal is closed</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>RepCalc_27</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>'Add to Project' popup shows both name fields, both options and buttons</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/Dividends/7% complete, clicking 'Add to Project' must open a popup with 'New Project'/'To an Existing Project' options, a 'Project Name' field (`input[name='project']`) AND a separate required 'Title' field (`input[name='name']`) - confirmed live these are two distinct required inputs (both happen to share the same duplicate `id='name'`, a real markup defect), not one.</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>User is logged in, AU-&gt;SG/Dividends/7% completed on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, complete AU-&gt;SG/Dividends/7%
 2. Click 'Add to Project'
 3. Verify the popup's expected elements</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/Dividends/7% complete, clicking 'Add to Project' must open a popup with 'New Project'/'To an Existing Project' options, a 'Project Name' field (`input[name='project']`) AND a separate required 'Title' field (`input[name='name']`) - confirmed live these are two distinct required inputs (both happen to share the same duplicate `id='name'`, a real markup defect), not one.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>The 'Add to Project' popup correctly showed all expected elements.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>[PASS] Add to Project popup shows all expected elements</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_28</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>'Add to Project' can create a new project from the calculation</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>With AU-&gt;SG/Dividends/7% complete, creating a uniquely-named new project via 'Add to Project' must succeed. Confirmed live the dialog has TWO required fields - 'Project Name' (`input[name='project']`) and 'Title' (`input[name='name']`) - both must be filled; submitting fires 'POST .../api/Project/AddToProject' returning `{"isSuccess":true}` (captured directly, since `page.request` calls bypass the app's JWT bearer auth and get a 401 - the browser's own authenticated request is the only reliable signal here). Cleanup re-uses the proven Tools &gt; Projects delete flow rather than an unauthenticated direct API call.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, AU-&gt;SG/Dividends/7% completed on Repatriation Calculator.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Project name: RepCalcQA_1791888109</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator, complete AU-&gt;SG/Dividends/7%
+2. Open 'Add to Project', fill both 'Project Name' and 'Title', click 'Add'
+3. Verify the real AddToProject response
+4. Clean up via Tools &gt; Projects</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>With AU-&gt;SG/Dividends/7% complete, creating a uniquely-named new project via 'Add to Project' must succeed. Confirmed live the dialog has TWO required fields - 'Project Name' (`input[name='project']`) and 'Title' (`input[name='name']`) - both must be filled; submitting fires 'POST .../api/Project/AddToProject' returning `{"isSuccess":true}` (captured directly, since `page.request` calls bypass the app's JWT bearer auth and get a 401 - the browser's own authenticated request is the only reliable signal here). Cleanup re-uses the proven Tools &gt; Projects delete flow rather than an unauthenticated direct API call.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>'Add to Project' correctly created project 'RepCalcQA_1791888109', confirmed via its real AddToProject response ({'isSuccess': True}).</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Add to Project' fires a 200 AddToProject call reporting isSuccess:true</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>RepCalc_29</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>'Start over' shows a confirmation dialog before resetting</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Start over' must show 'Are you sure to reset all your selections?' with Cancel/Yes buttons, not reset immediately.</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Repatriation Calculator
 2. Click 'Start over'
 3. Verify the confirmation dialog</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Start over' must show 'Are you sure to reset all your selections?' with Cancel/Yes buttons, not reset immediately.</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>'Start over' correctly showed a confirmation dialog before resetting.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Start over' shows a confirmation dialog with Cancel/Yes</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>RepCalc_30</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>'Start over' &gt; Cancel keeps the current selections</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>With Australia selected as Source Jurisdiction, clicking 'Start over' then 'Cancel' must leave Australia still selected.</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected as Source Jurisdiction.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Source: Australia</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select Australia as Source
 2. Click 'Start over' then 'Cancel'
 3. Verify Australia is still selected</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>With Australia selected as Source Jurisdiction, clicking 'Start over' then 'Cancel' must leave Australia still selected.</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Cancelling 'Start over' correctly left the current selections intact.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>[PASS] Cancelling 'Start over' leaves the current selection intact</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>RepCalc_31</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>'Start over' &gt; Yes resets the form to its placeholder state</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/100000 set, confirming 'Start over' must reset Source/Residence Jurisdiction back to 'Select' and clear the Repatriation Amount.</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia+Singapore+100000 set on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select Australia, Singapore and enter 100000
 2. Click 'Start over' then 'Yes'
 3. Verify the form reset to its placeholder state</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/100000 set, confirming 'Start over' must reset Source/Residence Jurisdiction back to 'Select' and clear the Repatriation Amount.</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>'Start over' &gt; Yes correctly reset the form to its placeholder state.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Start over' &gt; Yes resets the form to its placeholder state</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>RepCalc_32</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Selecting 'By Entity' switches the form to Corporate Group/Company fields</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Clicking 'By Entity' must replace Source/Residence Jurisdiction with Corporate Group and Source/Residence Company fields.</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Repatriation Calculator
 2. Click 'By Entity'
 3. Verify Corporate Group/Source Company/Residence Company fields appear</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Clicking 'By Entity' must replace Source/Residence Jurisdiction with Corporate Group and Source/Residence Company fields.</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Selecting 'By Entity' correctly switched to the Corporate Group/Company fields.</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'By Entity' mode shows Corporate Group/Company fields instead of jurisdiction fields</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>RepCalc_33</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Corporate Group dropdown lists this account's real entity charts</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>The Corporate Group dropdown (By Entity mode) must list real, account-specific entity charts, including the known 'Demo Entity Chart'.</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>User is logged in, 'By Entity' mode selected on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select 'By Entity'
 2. Open the Corporate Group dropdown
 3. Verify 'Demo Entity Chart' is listed</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>The Corporate Group dropdown (By Entity mode) must list real, account-specific entity charts, including the known 'Demo Entity Chart'.</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>The Corporate Group dropdown did not list the expected real entity charts (got ['Dummy', 'Natmed', 'Finanzas FMH Group', 'For Torrecid BD File', 'SMS Company', 'Parent-Test', 'Test without UPE', 'Test-001', 'Test-0000152', 'Empty Chart v1.7.2', 'Handy Home', 'Pillar two demo', 'Handy Home-P2', 'TEST-1', 'RETEST', 'Retest-1', 'P2 Test', 'Dummy-2']).</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>[FAIL] Corporate Group lists real entity charts including 'Demo Entity Chart'</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>The Corporate Group dropdown correctly listed 20 real entity charts, including 'Demo Entity Chart'.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Corporate Group lists real entity charts including 'Demo Entity Chart'</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_34</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Source/Residence Company options populate from the selected entity chart</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>After selecting 'Demo Entity Chart' as Corporate Group, both Source Company and Residence Company dropdowns must list that chart's real entities.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, 'By Entity' mode + 'Demo Entity Chart' selected.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Group: Demo Entity Chart</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator, select 'By Entity' and 'Demo Entity Chart'
+2. Open Source Company and Residence Company dropdowns
+3. Verify both list the same real entity set for that chart</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>After selecting 'Demo Entity Chart' as Corporate Group, both Source Company and Residence Company dropdowns must list that chart's real entities.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Source and Residence Company both correctly populated with 30 real entities from 'Demo Entity Chart'.</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Source/Residence Company both list the same real entity set</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_35</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>A no-treaty entity pairing shows a real informational warning, not a crash</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Selecting 'Rudyard William' as Source Company and '3rd party2 new' as Residence Company (confirmed live: no treaty between their underlying countries) must show a modal reading 'No treaty rate is available between ... Only domestic rate will apply.' - distinct from the blocking same-jurisdiction message, this is informational and the calculation proceeds using the domestic rate alone.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, 'By Entity' + 'Demo Entity Chart' selected.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Source Company: Rudyard William, Residence Company: 3rd party2 new</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator, select 'By Entity' and 'Demo Entity Chart'
+2. Select 'Rudyard William' as Source Company and '3rd party2 new' as Residence Company
+3. Verify the 'no treaty rate available' informational message</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Selecting 'Rudyard William' as Source Company and '3rd party2 new' as Residence Company (confirmed live: no treaty between their underlying countries) must show a modal reading 'No treaty rate is available between ... Only domestic rate will apply.' - distinct from the blocking same-jurisdiction message, this is informational and the calculation proceeds using the domestic rate alone.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>The no-treaty entity pairing correctly showed the real informational warning message.</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The no-treaty entity pairing shows the real informational warning</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_36</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Switching back to 'By Jurisdiction' resets the entity-specific selections</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>After selecting 'By Entity' and 'Demo Entity Chart', switching back to 'By Jurisdiction' must show the jurisdiction fields again with no leftover entity selection, rather than mixing state between modes.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, 'By Entity' + 'Demo Entity Chart' selected.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator, select 'By Entity' and 'Demo Entity Chart'
+2. Switch back to 'By Jurisdiction'
+3. Verify the jurisdiction fields show no leftover entity data</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>After selecting 'By Entity' and 'Demo Entity Chart', switching back to 'By Jurisdiction' must show the jurisdiction fields again with no leftover entity selection, rather than mixing state between modes.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Switching back to 'By Jurisdiction' correctly reset the entity-specific selections.</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Switching back to 'By Jurisdiction' resets entity selections</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>

--- a/test_data/WTA/WTA Calculator - Repatriation Calculator/WTA Calculator - Repatriation Calculator_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Calculator - Repatriation Calculator/WTA Calculator - Repatriation Calculator_Test_Cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,11 +47,6 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -65,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -74,9 +69,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -444,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,35 +512,151 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>RepCalc_01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Repatriation Calculator opens from the Calculators dropdown</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Repatriation Calculator' in the Calculators dropdown must land on /wta/RepCalculator with the heading and instructions banner visible.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Calculators &gt; Repatriation Calculator
+2. Verify the URL, page heading and instructions banner</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Repatriation Calculator' in the Calculators dropdown must land on /wta/RepCalculator with the heading and instructions banner visible.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Repatriation Calculator opened correctly with its heading and instructions visible.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Repatriation Calculator page loads with heading and instructions</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Initial state: 'By Jurisdiction' selected, action buttons disabled</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>On first load, 'By Jurisdiction' must be the checked mode and Generate Memo/Get Forms/Add to Project must all be disabled until enough of the form is completed.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Repatriation Calculator
+2. Verify 'By Jurisdiction' is checked and all 3 action buttons are disabled</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>On first load, 'By Jurisdiction' must be the checked mode and Generate Memo/Get Forms/Add to Project must all be disabled until enough of the form is completed.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>The calculator correctly starts on 'By Jurisdiction' with all action buttons disabled.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'By Jurisdiction' checked and all action buttons disabled initially</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>RepCalc_03</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Source Jurisdiction dropdown lists real countries and supports search</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Opening the Source Jurisdiction select must show a real, searchable country list (120 countries confirmed live); typing 'austra' must filter it to just Australia.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Search term: austra</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Repatriation Calculator
 2. Open the Source Jurisdiction select
@@ -556,59 +664,59 @@
 4. Verify the list filters to just Australia</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Opening the Source Jurisdiction select must show a real, searchable country list (120 countries confirmed live); typing 'austra' must filter it to just Australia.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Source Jurisdiction listed 108 real countries and correctly filtered to just Australia when searched.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Source Jurisdiction listed 120 real countries and correctly filtered to just Australia when searched.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>[PASS] Country list starts large and search filters to exactly 'Australia'</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>RepCalc_04</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Selecting a Source Jurisdiction sets the Repatriation Amount currency badge</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Before any selection the amount field shows a '--' placeholder badge; selecting Australia as Source Jurisdiction must update it to 'AUD' - a real dependent-field effect.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Country: Australia</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Repatriation Calculator
 2. Verify the currency badge starts as '--'
@@ -616,117 +724,176 @@
 4. Verify the currency badge becomes 'AUD'</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Before any selection the amount field shows a '--' placeholder badge; selecting Australia as Source Jurisdiction must update it to 'AUD' - a real dependent-field effect.</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>The currency badge correctly updated from '--' to 'AUD' as a dependent effect of the Source Jurisdiction selection.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>[PASS] Currency badge updates from '--' to 'AUD' after selecting Australia</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Selecting both jurisdictions renders the 'Relief from double taxation' panel</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>With Australia (source) and Singapore (residence) selected, a 'Relief from double taxation: Singapore' panel must render.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Repatriation Calculator.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Source: Australia, Residence: Singapore</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Repatriation Calculator
+2. Select Australia then Singapore
+3. Verify the Relief panel heading</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>With Australia (source) and Singapore (residence) selected, a 'Relief from double taxation: Singapore' panel must render.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Selecting both jurisdictions correctly rendered the Relief panel.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Relief from double taxation: Singapore' panel is visible</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>RepCalc_06</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Relief methods listed match the real AU-SG treaty data</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>The Relief panel's 'Relief methods' list for Australia/Singapore must show both 'Exemption' and 'Credit' - confirmed live, real treaty content, not placeholder text.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia+Singapore selected on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Source: Australia, Residence: Singapore</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select Australia and Singapore
 2. Verify the Relief methods list shows 'Exemption' and 'Credit'</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>The Relief panel's 'Relief methods' list for Australia/Singapore must show both 'Exemption' and 'Credit' - confirmed live, real treaty content, not placeholder text.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>The Relief methods list correctly showed both 'Exemption' and 'Credit' for AU/SG.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>[PASS] Relief methods list shows 'Exemption' and 'Credit'</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>RepCalc_07</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>'Get Forms' becomes enabled once a Source Jurisdiction is selected</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>'Get Forms' must stay disabled with nothing selected, and become enabled as soon as a Source Jurisdiction alone is picked - confirmed live this does NOT require a Residence Jurisdiction too (unlike Generate Memo/Add to Project, which need the full calculation chain); it stays enabled once Residence is added as well.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Source: Australia, Residence: Singapore</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator
 2. Verify 'Get Forms' starts disabled
@@ -735,709 +902,887 @@
 5. Select Singapore as Residence Jurisdiction and verify it stays enabled</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>'Get Forms' must stay disabled with nothing selected, and become enabled as soon as a Source Jurisdiction alone is picked - confirmed live this does NOT require a Residence Jurisdiction too (unlike Generate Memo/Add to Project, which need the full calculation chain); it stays enabled once Residence is added as well.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>'Get Forms' correctly enabled as soon as Source Jurisdiction alone was selected, and stayed enabled once Residence Jurisdiction was added too.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Get Forms' is disabled with nothing selected
 [PASS] 'Get Forms' becomes enabled once Source Jurisdiction alone is selected
 [PASS] 'Get Forms' remains enabled once Residence Jurisdiction is also selected</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>RepCalc_08</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Selecting the same country for both jurisdictions shows a blocking message</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Selecting 'Australia' as both Source and Residence Jurisdiction must trigger a modal reading 'Source and Residence Jurisdiction must be different.' with only a Cancel action - confirmed live real validation, not a crash or silent no-op.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected as Source Jurisdiction.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Source: Australia, Residence: Australia</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select Australia as Source
 2. Select Australia as Residence too
 3. Verify the blocking message modal</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Selecting 'Australia' as both Source and Residence Jurisdiction must trigger a modal reading 'Source and Residence Jurisdiction must be different.' with only a Cancel action - confirmed live real validation, not a crash or silent no-op.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Selecting the same country for both jurisdictions correctly triggered the real blocking validation message.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>[PASS] The same-jurisdiction validation modal shows the expected message with only Cancel</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>RepCalc_09</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Repatriation Amount rejects a negative sign (real keystrokes)</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Typing '-5000' (as real keystrokes, not .fill()) into Repatriation Amount must strip the minus sign - the field never holds a negative value.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Typed: -5000</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Repatriation Calculator
 2. Type '-5000' into Repatriation Amount
 3. Verify the minus sign was stripped</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Typing '-5000' (as real keystrokes, not .fill()) into Repatriation Amount must strip the minus sign - the field never holds a negative value.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Typing '-5000' correctly produced a non-negative value ('5,000').</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>[PASS] Repatriation Amount never holds a negative value</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>RepCalc_10</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Repatriation Amount strips non-digit characters</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Typing 'abc123' (real keystrokes) must leave only the digits ('123').</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Typed: abc123</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Repatriation Calculator
 2. Type 'abc123' into Repatriation Amount
 3. Verify only '123' remains</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Typing 'abc123' (real keystrokes) must leave only the digits ('123').</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Typing 'abc123' correctly left only the digits ('123').</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>[PASS] Only the digits '123' remain after typing 'abc123'</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>RepCalc_11</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Repatriation Amount treats '0' as no value</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Typing '0' alone must leave the field empty, confirming zero is rejected as a valid repatriation amount rather than being accepted as a literal zero.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Typed: 0</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Repatriation Calculator
 2. Type '0' into Repatriation Amount
 3. Verify the field is empty</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Typing '0' alone must leave the field empty, confirming zero is rejected as a valid repatriation amount rather than being accepted as a literal zero.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Typing '0' correctly left the amount field empty, confirming zero is treated as no value.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>[PASS] Typing '0' leaves Repatriation Amount empty</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>RepCalc_12</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Repatriation Amount accepts decimal values</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Typing '12.345' must be accepted as-is (decimal repatriation amounts are valid).</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Typed: 12.345</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Repatriation Calculator
 2. Type '12.345' into Repatriation Amount
 3. Verify the decimal value is retained</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Typing '12.345' must be accepted as-is (decimal repatriation amounts are valid).</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Typing '12.345' was correctly retained as a decimal value.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>[PASS] Decimal value '12.345' is retained</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>RepCalc_13</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Repatriation Amount formats large values with thousands separators</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Typing '1000000000' (one billion) must be accepted and displayed as '1,000,000,000' - confirmed live there is no artificial maximum blocking this.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Typed: 1000000000</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Repatriation Calculator
 2. Type '1000000000' into Repatriation Amount
 3. Verify it is formatted with thousands separators</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Typing '1000000000' (one billion) must be accepted and displayed as '1,000,000,000' - confirmed live there is no artificial maximum blocking this.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>A one-billion repatriation amount was correctly formatted as '1,000,000,000'.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>[PASS] Large value is formatted with thousands separators</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>RepCalc_14</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Income Stream dropdown lists the 5 real categories</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>The Select Income Stream dropdown must list exactly: Dividends, Interest, Royalties, Lease Payments, Technical Service Fees.</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>User is logged in, both jurisdictions and an amount set on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select Australia, Singapore and an amount
 2. Open the Select Income Stream dropdown
 3. Verify all 5 categories are listed</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>The Select Income Stream dropdown must list exactly: Dividends, Interest, Royalties, Lease Payments, Technical Service Fees.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>The Income Stream dropdown correctly listed all 5 categories: ['Dividends', 'Interest', 'Royalties', 'Lease Payments', 'Technical Service Fees'].</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>[PASS] Income Stream dropdown lists exactly the 5 expected categories</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Entering amount and income stream renders the results table</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>With Australia/Singapore/100,000/Dividends set, a results table with a 'What is the % of holding in the company?' selector must render.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Repatriation Calculator.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Source: Australia, Residence: Singapore, Amount: 100000, Stream: Dividends</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator
+2. Select Australia, Singapore, enter 100000, select Dividends
+3. Verify the results table with the holding % selector renders</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>With Australia/Singapore/100,000/Dividends set, a results table with a 'What is the % of holding in the company?' selector must render.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>The results table correctly rendered with the holding % selector.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The results table with the holding % question is visible</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>RepCalc_16</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Holding % selector is limited to exactly 1% through 7%</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>The 'What is the % of holding in the company?' dropdown must list exactly ['1%'..'7%'] - a real, confirmed-live data boundary, not a UI truncation.</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia/Singapore/100000/Dividends set.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, complete the setup through Income Stream
 2. Open the holding % dropdown
 3. Verify it lists exactly 1% through 7%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>The 'What is the % of holding in the company?' dropdown must list exactly ['1%'..'7%'] - a real, confirmed-live data boundary, not a UI truncation.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>The holding % dropdown correctly listed exactly ['1%', '2%', '3%', '4%', '5%', '6%', '7%'].</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>[PASS] Holding % dropdown lists exactly 1% through 7%</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>The displayed Treaty Rate matches the live Treaty API</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>With Australia/Singapore/Dividends/7% selected, the UI must show 'Treaty Rate - 15.00%' and 'Your holding type is Portfolio.' - independently verified against GET /api/Treaty?hostCountryCode=AU&amp;partnerCountryCode=SG (WtrDomesticRates[Portfolio Dividend].Rate), not compared against itself.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Repatriation Calculator.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Source: Australia, Residence: Singapore, Stream: Dividends, Holding: 7%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator, complete AU-&gt;SG/Dividends/7%
+2. Independently fetch the Treaty API for AU/SG
+3. Verify the UI's Treaty Rate matches the API's Portfolio Dividend rate</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>With Australia/Singapore/Dividends/7% selected, the UI must show 'Treaty Rate - 15.00%' and 'Your holding type is Portfolio.' - independently verified against GET /api/Treaty?hostCountryCode=AU&amp;partnerCountryCode=SG (WtrDomesticRates[Portfolio Dividend].Rate), not compared against itself.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>The UI's Treaty Rate ('Treaty Rate - 15.00%') correctly matched the live API's independent value (15.00%).</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] UI Treaty Rate matches the independently-fetched API value</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Withholding tax amount matches an independent Python calculation</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>With amount=100,000, Treaty Rate=15.00% and a user-entered Exchange Rate of 1.2, the computed Withholding tax amount AND Total Tax Due must both equal 100,000 x 0.15 x 1.2 = 18,000 - calculated independently in Python from the known inputs, not read back from the application and compared to itself.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, AU-&gt;SG/Dividends/7% completed on Repatriation Calculator.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Amount: 100000, Treaty Rate: 15%, Exchange Rate: 1.2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator, complete AU-&gt;SG/Dividends/7% with amount 100000
+2. Enter Exchange Rate = 1.2
+3. Independently compute 100000 x 0.15 x 1.2
+4. Verify both the Withholding tax amount and Total Tax Due equal that value</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>With amount=100,000, Treaty Rate=15.00% and a user-entered Exchange Rate of 1.2, the computed Withholding tax amount AND Total Tax Due must both equal 100,000 x 0.15 x 1.2 = 18,000 - calculated independently in Python from the known inputs, not read back from the application and compared to itself.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>The computed amounts (18000, 18000) correctly matched the independent calculation of 18,000 (100,000 x 15% x 1.2).</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Withholding tax amount and Total Tax Due match the independent Python calculation</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>RepCalc_19</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Changing the Exchange Rate live-recalculates the computed amounts</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>After computing with Exchange Rate=1.2 (18,000), changing it to 2.0 must update the Withholding tax amount/Total Tax Due to 100,000 x 0.15 x 2.0 = 30,000 without requiring any other field to be re-entered.</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>User is logged in, AU-&gt;SG/Dividends/7%/Exchange Rate=1.2 completed.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Exchange Rate changed from 1.2 to 2.0</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, complete the setup with Exchange Rate 1.2
 2. Change the Exchange Rate to 2.0
 3. Verify the computed amounts update to 30,000</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>After computing with Exchange Rate=1.2 (18,000), changing it to 2.0 must update the Withholding tax amount/Total Tax Due to 100,000 x 0.15 x 2.0 = 30,000 without requiring any other field to be re-entered.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Changing the Exchange Rate correctly recalculated the amounts to 30,000.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>[PASS] Changing the Exchange Rate live-recalculates the computed amounts</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>RepCalc_20</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>The Rates panel shows the real treaty article text</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>The 'Rates: Australia' panel must show 'Article 8 (1)' and the real treaty wording mentioning 'shall not exceed 15 per centum of the gross amount of the dividends.'</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>User is logged in, AU-&gt;SG/Dividends/7% completed on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, complete AU-&gt;SG/Dividends/7%
 2. Verify the Rates panel shows Article 8(1) and the treaty wording</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>The 'Rates: Australia' panel must show 'Article 8 (1)' and the real treaty wording mentioning 'shall not exceed 15 per centum of the gross amount of the dividends.'</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>The Rates panel correctly showed the real Article 8(1) treaty wording.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>[PASS] Rates panel shows the real Article 8(1) treaty text</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>RepCalc_21</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Switching Income Stream resets the holding %/rate selection</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>After selecting Dividends and a 7% holding (Treaty Rate 15.00%), switching Income Stream to 'Interest' must clear the previous holding %/rate selection rather than carry stale Dividend-specific data forward.</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>User is logged in, AU-&gt;SG/Dividends/7% completed on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Stream changed from Dividends to Interest</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, complete AU-&gt;SG/Dividends/7%
 2. Change Income Stream to 'Interest'
 3. Verify the Dividend-specific holding type text is no longer shown</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>After selecting Dividends and a 7% holding (Treaty Rate 15.00%), switching Income Stream to 'Interest' must clear the previous holding %/rate selection rather than carry stale Dividend-specific data forward.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Switching Income Stream correctly reset the previous selection's holding-type text.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>[PASS] Switching Income Stream clears the previous stream's holding selection</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>RepCalc_22</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>'Generate Memo'/'Add to Project' enable only after the full chain completes</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Both buttons must stay disabled through jurisdictions+amount+stream, and only become enabled once a holding % is also selected (the full calculation chain).</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, complete jurisdictions+amount+stream only
 2. Verify Generate Memo/Add to Project are still disabled
@@ -1445,296 +1790,355 @@
 4. Verify both become enabled</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Both buttons must stay disabled through jurisdictions+amount+stream, and only become enabled once a holding % is also selected (the full calculation chain).</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>'Generate Memo'/'Add to Project' correctly followed the full-chain dependency.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>[PASS] Generate Memo/Add to Project disabled before holding % is selected
 [PASS] Generate Memo/Add to Project become enabled once holding % is selected</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>RepCalc_23</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>'Generate Memo' downloads a real, non-empty .docx file</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/Dividends/7% complete, clicking 'Generate Memo' must download a real, non-empty .docx memo.</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>User is logged in, AU-&gt;SG/Dividends/7% completed on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, complete AU-&gt;SG/Dividends/7%
 2. Click 'Generate Memo'
 3. Verify a real, non-empty .docx download completed</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/Dividends/7% complete, clicking 'Generate Memo' must download a real, non-empty .docx memo.</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>'Generate Memo' correctly downloaded 'AU_SG_Repatriation_Calculator_Memo.docx' (9067 bytes).</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>'Generate Memo' correctly downloaded 'AU_SG_Repatriation_Calculator_Memo.docx' (9068 bytes).</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>[PASS] Generate Memo produces a real, non-empty .docx file with no failure</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>RepCalc_24</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>'Get Forms' opens a modal with the real, jurisdiction-specific form list</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>With Australia/Singapore selected, clicking 'Get Forms' must open a modal reading 'CIT Returns and WHT deduction/Treaty form of Australia.' with a real Title/Description/Application Date/Last Reviewed/Download table.</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia+Singapore selected on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select Australia and Singapore
 2. Click 'Get Forms'
 3. Verify the modal shows the real form list</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>With Australia/Singapore selected, clicking 'Get Forms' must open a modal reading 'CIT Returns and WHT deduction/Treaty form of Australia.' with a real Title/Description/Application Date/Last Reviewed/Download table.</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>The 'Get Forms' modal did not show the expected real content.</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>[FAIL] 'Get Forms' modal shows the real jurisdiction-specific form list</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>'Get Forms' correctly opened with the real, jurisdiction-specific form list.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Get Forms' modal shows the real jurisdiction-specific form list</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>A form's download link in 'Get Forms' downloads a real, non-empty file</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Inside the 'Get Forms' modal, clicking the first 'English' download link must trigger a real, non-empty file download.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia+Singapore selected, 'Get Forms' modal open.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator, select Australia+Singapore, open 'Get Forms'
+2. Click the first 'English' download link
+3. Verify a real, non-empty download completed</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Inside the 'Get Forms' modal, clicking the first 'English' download link must trigger a real, non-empty file download.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>The form download link correctly downloaded 'AU_Form__NAT_0656_06_2025_English_pdf.pdf' (1056759 bytes).</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The form's download link produces a real, non-empty file with no failure</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>RepCalc_26</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>The 'Get Forms' modal's Close button closes it</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>With the 'Get Forms' modal open, clicking 'Close' must close it.</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia+Singapore selected, 'Get Forms' modal open.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select Australia+Singapore, open 'Get Forms'
 2. Click 'Close'
 3. Verify the modal is closed</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>With the 'Get Forms' modal open, clicking 'Close' must close it.</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>The 'Get Forms' modal's Close button correctly closed it.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>[PASS] The 'Get Forms' modal is closed</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>RepCalc_27</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>'Add to Project' popup shows both name fields, both options and buttons</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/Dividends/7% complete, clicking 'Add to Project' must open a popup with 'New Project'/'To an Existing Project' options, a 'Project Name' field (`input[name='project']`) AND a separate required 'Title' field (`input[name='name']`) - confirmed live these are two distinct required inputs (both happen to share the same duplicate `id='name'`, a real markup defect), not one.</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>User is logged in, AU-&gt;SG/Dividends/7% completed on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, complete AU-&gt;SG/Dividends/7%
 2. Click 'Add to Project'
 3. Verify the popup's expected elements</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/Dividends/7% complete, clicking 'Add to Project' must open a popup with 'New Project'/'To an Existing Project' options, a 'Project Name' field (`input[name='project']`) AND a separate required 'Title' field (`input[name='name']`) - confirmed live these are two distinct required inputs (both happen to share the same duplicate `id='name'`, a real markup defect), not one.</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>The 'Add to Project' popup correctly showed all expected elements.</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>[PASS] Add to Project popup shows all expected elements</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>RepCalc_28</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>'Add to Project' can create a new project from the calculation</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/Dividends/7% complete, creating a uniquely-named new project via 'Add to Project' must succeed. Confirmed live the dialog has TWO required fields - 'Project Name' (`input[name='project']`) and 'Title' (`input[name='name']`) - both must be filled; submitting fires 'POST .../api/Project/AddToProject' returning `{"isSuccess":true}` (captured directly, since `page.request` calls bypass the app's JWT bearer auth and get a 401 - the browser's own authenticated request is the only reliable signal here). Cleanup re-uses the proven Tools &gt; Projects delete flow rather than an unauthenticated direct API call.</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>User is logged in, AU-&gt;SG/Dividends/7% completed on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Project name: RepCalcQA_1792044940</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Project name: RepCalcQA_1793014404</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, complete AU-&gt;SG/Dividends/7%
 2. Open 'Add to Project', fill both 'Project Name' and 'Title', click 'Add'
@@ -1742,201 +2146,496 @@
 4. Clean up via Tools &gt; Projects</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/Dividends/7% complete, creating a uniquely-named new project via 'Add to Project' must succeed. Confirmed live the dialog has TWO required fields - 'Project Name' (`input[name='project']`) and 'Title' (`input[name='name']`) - both must be filled; submitting fires 'POST .../api/Project/AddToProject' returning `{"isSuccess":true}` (captured directly, since `page.request` calls bypass the app's JWT bearer auth and get a 401 - the browser's own authenticated request is the only reliable signal here). Cleanup re-uses the proven Tools &gt; Projects delete flow rather than an unauthenticated direct API call.</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>'Add to Project' correctly created project 'RepCalcQA_1792044940', confirmed via its real AddToProject response ({'isSuccess': True}).</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>'Add to Project' correctly created project 'RepCalcQA_1793014404', confirmed via its real AddToProject response ({'isSuccess': True}).</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Add to Project' fires a 200 AddToProject call reporting isSuccess:true</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_29</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>'Start over' shows a confirmation dialog before resetting</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Start over' must show 'Are you sure to reset all your selections?' with Cancel/Yes buttons, not reset immediately.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Repatriation Calculator.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Repatriation Calculator
+2. Click 'Start over'
+3. Verify the confirmation dialog</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Start over' must show 'Are you sure to reset all your selections?' with Cancel/Yes buttons, not reset immediately.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>'Start over' correctly showed a confirmation dialog before resetting.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Start over' shows a confirmation dialog with Cancel/Yes</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>RepCalc_30</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>'Start over' &gt; Cancel keeps the current selections</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>With Australia selected as Source Jurisdiction, clicking 'Start over' then 'Cancel' must leave Australia still selected.</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected as Source Jurisdiction.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Source: Australia</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select Australia as Source
 2. Click 'Start over' then 'Cancel'
 3. Verify Australia is still selected</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>With Australia selected as Source Jurisdiction, clicking 'Start over' then 'Cancel' must leave Australia still selected.</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Cancelling 'Start over' correctly left the current selections intact.</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>[PASS] Cancelling 'Start over' leaves the current selection intact</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>RepCalc_31</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>'Start over' &gt; Yes resets the form to its placeholder state</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/100000 set, confirming 'Start over' must reset Source/Residence Jurisdiction back to 'Select' and clear the Repatriation Amount.</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia+Singapore+100000 set on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select Australia, Singapore and enter 100000
 2. Click 'Start over' then 'Yes'
 3. Verify the form reset to its placeholder state</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>With AU-&gt;SG/100000 set, confirming 'Start over' must reset Source/Residence Jurisdiction back to 'Select' and clear the Repatriation Amount.</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>'Start over' &gt; Yes correctly reset the form to its placeholder state.</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Start over' &gt; Yes resets the form to its placeholder state</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_32</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Selecting 'By Entity' switches the form to Corporate Group/Company fields</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'By Entity' must replace Source/Residence Jurisdiction with Corporate Group and Source/Residence Company fields.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Repatriation Calculator.</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Repatriation Calculator
+2. Click 'By Entity'
+3. Verify Corporate Group/Source Company/Residence Company fields appear</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'By Entity' must replace Source/Residence Jurisdiction with Corporate Group and Source/Residence Company fields.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Selecting 'By Entity' correctly switched to the Corporate Group/Company fields.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'By Entity' mode shows Corporate Group/Company fields instead of jurisdiction fields</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>RepCalc_33</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Repatriation Calculator</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Corporate Group dropdown lists this account's real entity charts</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>The Corporate Group dropdown (By Entity mode) must list real, account-specific entity charts, including the known 'Demo Entity Chart'.</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>User is logged in, 'By Entity' mode selected on Repatriation Calculator.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Repatriation Calculator, select 'By Entity'
 2. Open the Corporate Group dropdown
 3. Verify 'Demo Entity Chart' is listed</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>The Corporate Group dropdown (By Entity mode) must list real, account-specific entity charts, including the known 'Demo Entity Chart'.</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>The Corporate Group dropdown did not list the expected real entity charts (got ['Handy Home AG', 'Netflix Inc', 'TESTTTTTTT', 'TESTTTT fu', 'testt qa', 'dsf', 'Hoichoi Inc.', 'Handy Home 2', 'REAL TEST', 'TEST NEW']).</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>[FAIL] Corporate Group lists real entity charts including 'Demo Entity Chart'</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>The Corporate Group dropdown correctly listed 20 real entity charts, including 'Demo Entity Chart'.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Corporate Group lists real entity charts including 'Demo Entity Chart'</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_34</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Source/Residence Company options populate from the selected entity chart</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>After selecting 'Demo Entity Chart' as Corporate Group, both Source Company and Residence Company dropdowns must list that chart's real entities.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, 'By Entity' mode + 'Demo Entity Chart' selected.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Group: Demo Entity Chart</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator, select 'By Entity' and 'Demo Entity Chart'
+2. Open Source Company and Residence Company dropdowns
+3. Verify both list the same real entity set for that chart</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>After selecting 'Demo Entity Chart' as Corporate Group, both Source Company and Residence Company dropdowns must list that chart's real entities.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Source and Residence Company both correctly populated with 32 real entities from 'Demo Entity Chart'.</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Source/Residence Company both list the same real entity set</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_35</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>A no-treaty entity pairing shows a real informational warning, not a crash</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Selecting 'Rudyard William' as Source Company and '3rd party2 new' as Residence Company (confirmed live: no treaty between their underlying countries) must show a modal reading 'No treaty rate is available between ... Only domestic rate will apply.' - distinct from the blocking same-jurisdiction message, this is informational and the calculation proceeds using the domestic rate alone.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, 'By Entity' + 'Demo Entity Chart' selected.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Source Company: Rudyard William, Residence Company: 3rd party2 new</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator, select 'By Entity' and 'Demo Entity Chart'
+2. Select 'Rudyard William' as Source Company and '3rd party2 new' as Residence Company
+3. Verify the 'no treaty rate available' informational message</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Selecting 'Rudyard William' as Source Company and '3rd party2 new' as Residence Company (confirmed live: no treaty between their underlying countries) must show a modal reading 'No treaty rate is available between ... Only domestic rate will apply.' - distinct from the blocking same-jurisdiction message, this is informational and the calculation proceeds using the domestic rate alone.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>The no-treaty entity pairing correctly showed the real informational warning message.</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The no-treaty entity pairing shows the real informational warning</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>RepCalc_36</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>WTA Calculator - Repatriation Calculator</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Switching back to 'By Jurisdiction' resets the entity-specific selections</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>After selecting 'By Entity' and 'Demo Entity Chart', switching back to 'By Jurisdiction' must show the jurisdiction fields again with no leftover entity selection, rather than mixing state between modes.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, 'By Entity' + 'Demo Entity Chart' selected.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Repatriation Calculator, select 'By Entity' and 'Demo Entity Chart'
+2. Switch back to 'By Jurisdiction'
+3. Verify the jurisdiction fields show no leftover entity data</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>After selecting 'By Entity' and 'Demo Entity Chart', switching back to 'By Jurisdiction' must show the jurisdiction fields again with no leftover entity selection, rather than mixing state between modes.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Switching back to 'By Jurisdiction' correctly reset the entity-specific selections.</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Switching back to 'By Jurisdiction' resets entity selections</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
